--- a/content/posts/harry-browne-permanent-portfolio/Stocks_Bonds_Gold_Cash_Annual_Returns.xlsx
+++ b/content/posts/harry-browne-permanent-portfolio/Stocks_Bonds_Gold_Cash_Annual_Returns.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,283 +413,299 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Return</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>1991</v>
       </c>
       <c r="B2" t="n">
-        <v>0.102105082723067</v>
+        <v>0.1164935222145635</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1992</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03032334528415737</v>
+        <v>0.03928464257238007</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>1993</v>
       </c>
       <c r="B4" t="n">
-        <v>0.09869511221702587</v>
+        <v>0.1064920094151636</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>1994</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.01722248131363235</v>
+        <v>-0.006122699020187472</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>1995</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1534732842575941</v>
+        <v>0.1680059640359024</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>1996</v>
       </c>
       <c r="B7" t="n">
-        <v>0.04852877287882129</v>
+        <v>0.06181622817251675</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>1997</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0561268523695444</v>
+        <v>0.06946939590658263</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>1998</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1021069235071073</v>
+        <v>0.1146679257251859</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>1999</v>
       </c>
       <c r="B10" t="n">
-        <v>0.03919609584560635</v>
+        <v>0.05136902052080838</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>2000</v>
       </c>
       <c r="B11" t="n">
-        <v>2.548080957986976e-05</v>
+        <v>0.0154246735194008</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>2001</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.005315046972770965</v>
+        <v>0.003657277119021973</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>2002</v>
       </c>
       <c r="B13" t="n">
-        <v>0.04265820146201094</v>
+        <v>0.04677755287233132</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>2003</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1209388787777452</v>
+        <v>0.1235212796646121</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>2004</v>
       </c>
       <c r="B15" t="n">
-        <v>0.05141938276759817</v>
+        <v>0.05491272626846766</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>2005</v>
       </c>
       <c r="B16" t="n">
-        <v>0.06423539756648577</v>
+        <v>0.07234550521118632</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>2006</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1043072030824377</v>
+        <v>0.1167274783054106</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>2007</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1171389472873836</v>
+        <v>0.128648586943326</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>2008</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.03338346840440498</v>
+        <v>-0.0298981840663437</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>2009</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1073540865110101</v>
+        <v>0.1077272814011196</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>2010</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1365503587509174</v>
+        <v>0.1368916595955192</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>2011</v>
       </c>
       <c r="B22" t="n">
-        <v>0.06968329402297591</v>
+        <v>0.06981373587824802</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>2012</v>
       </c>
       <c r="B23" t="n">
-        <v>0.06750673135540164</v>
+        <v>0.06772355369912897</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>2013</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.006023340949763201</v>
+        <v>-0.005881786291999314</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>2014</v>
       </c>
       <c r="B25" t="n">
-        <v>0.05226379020033489</v>
+        <v>0.05234404123345282</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>2015</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.01833193111356624</v>
+        <v>-0.01820443760874313</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>2016</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0524633732252493</v>
+        <v>0.05325910907569487</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>2017</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0949683975334239</v>
+        <v>0.09733339120349505</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>2018</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.01194918185689919</v>
+        <v>-0.006950147489315883</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>2019</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1453971013154693</v>
+        <v>0.1507149992551053</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>2020</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1339851311111731</v>
+        <v>0.1348912820055308</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>2021</v>
       </c>
       <c r="B32" t="n">
-        <v>0.05678626566879741</v>
+        <v>0.05689723704917116</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>2022</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.08242395496354504</v>
+        <v>-0.07725331567562144</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>2023</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1087613196234449</v>
+        <v>0.12228653865451</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.1424091103865375</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0.2366607878328697</v>
       </c>
     </row>
   </sheetData>
